--- a/data/trans_camb/IP19C02-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP19C02-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-27,59; 1,45</t>
+          <t>-26,97; 4,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-24,26; 4,99</t>
+          <t>-25,87; 4,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,54; 24,75</t>
+          <t>-15,72; 23,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,65; 7,74</t>
+          <t>-14,54; 9,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-19,7; 1,29</t>
+          <t>-18,22; 1,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 19,71</t>
+          <t>-9,96; 18,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-16,82; 1,96</t>
+          <t>-16,77; 2,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-16,07; 0,6</t>
+          <t>-16,44; 1,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 16,67</t>
+          <t>-6,96; 16,74</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-89,05; 140,13</t>
+          <t>-92,73; 81,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-74,95; 415,92</t>
+          <t>-74,04; 485,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -808,29 +808,29 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-77,58; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-91,55; 56,47</t>
+          <t>-90,62; 60,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-89,09; 40,77</t>
+          <t>-88,73; 40,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-50,75; 255,78</t>
+          <t>-50,59; 270,32</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,19; 10,59</t>
+          <t>1,17; 10,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,57</t>
+          <t>0,0; 7,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,31; 14,87</t>
+          <t>2,34; 14,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 4,5</t>
+          <t>-9,49; 3,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 12,81</t>
+          <t>-4,3; 11,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 11,21</t>
+          <t>-5,73; 10,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 4,42</t>
+          <t>-3,66; 4,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 8,28</t>
+          <t>-1,49; 8,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 9,79</t>
+          <t>-0,09; 10,54</t>
         </is>
       </c>
     </row>
@@ -1014,39 +1014,39 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 217,94</t>
+          <t>-100,0; 213,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-47,3; 425,59</t>
+          <t>-53,24; 355,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-61,71; 378,22</t>
+          <t>-63,72; 344,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-74,46; 271,33</t>
+          <t>-70,13; 295,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-37,5; 479,87</t>
+          <t>-40,72; 524,62</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-9,86; 626,65</t>
+          <t>-16,6; 682,79</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-15,62; 1,89</t>
+          <t>-14,7; 1,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,93; 17,19</t>
+          <t>-6,4; 15,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,41; 8,01</t>
+          <t>-10,66; 9,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 11,03</t>
+          <t>-3,49; 10,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 8,05</t>
+          <t>-3,62; 6,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 14,18</t>
+          <t>-1,76; 14,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 5,27</t>
+          <t>-5,33; 4,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 8,64</t>
+          <t>-4,07; 9,21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 8,96</t>
+          <t>-4,14; 8,46</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 911,54</t>
+          <t>-73,81; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-85,0; 661,35</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-70,07; 731,39</t>
+          <t>-72,84; 722,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-68,02; 672,83</t>
+          <t>-71,2; 508,08</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 4,01</t>
+          <t>-9,81; 4,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 18,17</t>
+          <t>-0,08; 18,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 18,68</t>
+          <t>-1,33; 18,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,14; 22,26</t>
+          <t>3,17; 20,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,66; 14,31</t>
+          <t>1,59; 14,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,04; 23,64</t>
+          <t>1,73; 25,34</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 9,54</t>
+          <t>-0,81; 10,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,76; 13,85</t>
+          <t>1,9; 13,07</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,26; 16,96</t>
+          <t>2,59; 17,28</t>
         </is>
       </c>
     </row>
@@ -1436,12 +1436,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-44,23; —</t>
+          <t>-41,69; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-61,35; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-73,33; —</t>
+          <t>-72,66; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-10,14; —</t>
+          <t>-12,61; —</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9,71; —</t>
+          <t>13,36; —</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-32,92; -1,71</t>
+          <t>-33,09; -1,21</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>20,98; 68,45</t>
+          <t>22,78; 71,43</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>28,21; 64,0</t>
+          <t>28,94; 65,05</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-21,95; 3,52</t>
+          <t>-22,39; 3,32</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>37,26; 79,74</t>
+          <t>39,29; 79,63</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>43,54; 75,81</t>
+          <t>43,45; 76,58</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-24,45; -2,79</t>
+          <t>-24,36; -2,86</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>38,02; 70,28</t>
+          <t>37,25; 69,21</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>41,84; 66,05</t>
+          <t>41,57; 65,83</t>
         </is>
       </c>
     </row>
@@ -1647,17 +1647,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 44,03</t>
+          <t>-100,0; 30,74</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>65,32; 531,54</t>
+          <t>64,5; 551,8</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>79,39; 507,36</t>
+          <t>78,64; 556,26</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1667,34 +1667,34 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>136,23; 2166,75</t>
+          <t>166,31; 2220,19</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>157,45; 2245,58</t>
+          <t>164,98; 2240,79</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-93,07; -12,54</t>
+          <t>-93,16; -3,09</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>138,93; 596,87</t>
+          <t>135,44; 611,12</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>147,36; 611,84</t>
+          <t>143,86; 572,41</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-9,74; 9,76</t>
+          <t>-10,61; 10,36</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>6,18; 36,07</t>
+          <t>6,46; 35,22</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-11,78; 7,43</t>
+          <t>-13,64; 5,86</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 15,75</t>
+          <t>-4,21; 14,96</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,49; 28,28</t>
+          <t>4,57; 30,17</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-12,77; 0,0</t>
+          <t>-13,1; 0,0</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 9,89</t>
+          <t>-5,28; 10,25</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>9,45; 28,09</t>
+          <t>8,76; 27,73</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-9,55; 1,73</t>
+          <t>-9,34; 1,79</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>17,76; —</t>
+          <t>6,06; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-16,29; —</t>
+          <t>-7,41; —</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1893,12 +1893,12 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-65,44; 548,41</t>
+          <t>-66,76; 769,1</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>83,79; 1752,5</t>
+          <t>58,74; 1676,76</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-10,16; 3,51</t>
+          <t>-9,52; 4,31</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 14,79</t>
+          <t>-2,2; 15,27</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 16,64</t>
+          <t>-0,66; 17,48</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-10,41; 2,71</t>
+          <t>-10,37; 2,97</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>8,0; 29,16</t>
+          <t>7,17; 29,59</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,46; 25,72</t>
+          <t>4,82; 25,45</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 1,68</t>
+          <t>-8,03; 1,37</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>5,08; 19,14</t>
+          <t>5,14; 18,72</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>5,09; 18,58</t>
+          <t>5,51; 19,49</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-89,25; 127,61</t>
+          <t>-86,2; 156,46</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-22,18; 390,45</t>
+          <t>-23,94; 376,89</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-18,78; 394,75</t>
+          <t>-11,6; 454,29</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-91,08; 116,23</t>
+          <t>-88,29; 136,84</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>60,62; 835,37</t>
+          <t>52,01; 880,11</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>21,44; 733,19</t>
+          <t>37,35; 713,5</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-77,77; 50,13</t>
+          <t>-77,04; 41,5</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>41,99; 399,05</t>
+          <t>46,31; 399,15</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>46,53; 391,59</t>
+          <t>45,28; 416,12</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 11,31</t>
+          <t>-3,92; 10,91</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>14,75; 33,99</t>
+          <t>15,17; 33,61</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>63,97; 81,15</t>
+          <t>64,02; 81,13</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-9,62; 6,29</t>
+          <t>-10,06; 5,8</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>11,72; 32,98</t>
+          <t>11,68; 32,2</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>62,06; 79,61</t>
+          <t>62,17; 79,18</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 6,59</t>
+          <t>-5,2; 5,77</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>16,01; 30,51</t>
+          <t>16,07; 29,91</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>65,61; 77,96</t>
+          <t>66,81; 78,82</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-41,36; 225,18</t>
+          <t>-36,98; 224,21</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>105,51; 648,83</t>
+          <t>127,84; 721,23</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>460,25; 1748,67</t>
+          <t>499,91; 1890,39</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-67,38; 89,94</t>
+          <t>-67,33; 88,0</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>66,82; 459,01</t>
+          <t>70,11; 432,47</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>357,14; 1153,27</t>
+          <t>364,22; 1147,7</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-36,04; 91,65</t>
+          <t>-43,45; 80,31</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>121,92; 456,18</t>
+          <t>122,07; 429,66</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>515,55; 1293,42</t>
+          <t>503,37; 1256,0</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 1,55</t>
+          <t>-4,69; 1,65</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>7,55; 15,62</t>
+          <t>7,84; 15,89</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>17,6; 26,88</t>
+          <t>17,83; 27,53</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 2,72</t>
+          <t>-3,35; 2,74</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>8,86; 16,75</t>
+          <t>8,77; 17,06</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>20,39; 29,93</t>
+          <t>20,17; 30,08</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 1,21</t>
+          <t>-3,19; 1,14</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>9,25; 14,93</t>
+          <t>9,57; 15,22</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>20,52; 27,09</t>
+          <t>20,2; 27,1</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-50,04; 28,52</t>
+          <t>-50,66; 29,71</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>81,22; 271,1</t>
+          <t>85,75; 277,32</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>195,61; 482,5</t>
+          <t>195,16; 490,86</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-39,01; 51,73</t>
+          <t>-40,42; 52,99</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>109,15; 321,82</t>
+          <t>105,21; 330,28</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>238,63; 593,22</t>
+          <t>233,43; 562,85</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-37,85; 20,54</t>
+          <t>-40,26; 18,37</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>112,14; 258,28</t>
+          <t>118,61; 253,58</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>250,88; 465,36</t>
+          <t>242,06; 445,98</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C02-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP19C02-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-26,97; 4,01</t>
+          <t>-27,63; 0,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-25,87; 4,37</t>
+          <t>-24,58; 3,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,72; 23,84</t>
+          <t>-16,2; 24,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,54; 9,34</t>
+          <t>-14,84; 8,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-18,22; 1,99</t>
+          <t>-19,73; 1,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,96; 18,17</t>
+          <t>-9,2; 17,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-16,77; 2,32</t>
+          <t>-15,9; 1,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-16,44; 1,1</t>
+          <t>-16,57; 0,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 16,74</t>
+          <t>-7,35; 16,04</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 217,97</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>-91,2; 118,87</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>-73,94; 548,52</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-92,73; 81,75</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-74,04; 485,91</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-77,64; 693,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-90,62; 60,4</t>
+          <t>-89,81; 55,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-88,73; 40,91</t>
+          <t>-91,02; 29,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-50,59; 270,32</t>
+          <t>-51,35; 270,74</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 10,07</t>
+          <t>0,0; 9,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,49</t>
+          <t>0,0; 7,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,34; 14,6</t>
+          <t>2,3; 14,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,49; 3,61</t>
+          <t>-9,9; 3,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 11,52</t>
+          <t>-3,69; 12,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 10,45</t>
+          <t>-4,27; 11,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 4,28</t>
+          <t>-3,88; 4,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 8,3</t>
+          <t>-1,34; 8,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 10,54</t>
+          <t>-0,34; 9,64</t>
         </is>
       </c>
     </row>
@@ -1014,32 +1014,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 213,87</t>
+          <t>-100,0; 153,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-53,24; 355,26</t>
+          <t>-48,66; 492,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-63,72; 344,19</t>
+          <t>-53,58; 403,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-70,13; 295,2</t>
+          <t>-77,67; 279,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-40,72; 524,62</t>
+          <t>-38,15; 666,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-16,6; 682,79</t>
+          <t>-28,16; 522,47</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,7; 1,92</t>
+          <t>-15,47; 1,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 15,67</t>
+          <t>-7,6; 14,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 9,47</t>
+          <t>-11,14; 9,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 10,76</t>
+          <t>-1,81; 12,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 6,79</t>
+          <t>-3,6; 6,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 14,22</t>
+          <t>-1,81; 14,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 4,89</t>
+          <t>-5,63; 4,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 9,21</t>
+          <t>-4,09; 8,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 8,46</t>
+          <t>-3,57; 8,71</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-73,81; —</t>
+          <t>-96,68; 762,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 470,67</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-72,84; 722,4</t>
+          <t>-75,41; 521,53</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-71,2; 508,08</t>
+          <t>-65,86; 652,17</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,81; 4,01</t>
+          <t>-8,56; 4,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 18,99</t>
+          <t>-0,53; 19,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 18,35</t>
+          <t>-1,6; 19,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,17; 20,22</t>
+          <t>3,13; 21,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,59; 14,12</t>
+          <t>1,62; 13,8</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,73; 25,34</t>
+          <t>2,46; 27,01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 10,32</t>
+          <t>-0,9; 10,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,9; 13,07</t>
+          <t>1,64; 13,31</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,59; 17,28</t>
+          <t>1,95; 17,55</t>
         </is>
       </c>
     </row>
@@ -1436,42 +1436,42 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-41,69; —</t>
+          <t>-45,19; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>-56,7; —</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-72,66; —</t>
+          <t>-60,26; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-12,61; —</t>
+          <t>5,63; —</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13,36; —</t>
+          <t>-7,47; —</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-33,09; -1,21</t>
+          <t>-33,04; -1,62</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>22,78; 71,43</t>
+          <t>23,59; 70,58</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>28,94; 65,05</t>
+          <t>27,19; 64,25</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-22,39; 3,32</t>
+          <t>-22,8; 3,56</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>39,29; 79,63</t>
+          <t>37,42; 78,74</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>43,45; 76,58</t>
+          <t>44,55; 77,1</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-24,36; -2,86</t>
+          <t>-23,85; -2,53</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>37,25; 69,21</t>
+          <t>36,04; 68,31</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>41,57; 65,83</t>
+          <t>41,66; 65,53</t>
         </is>
       </c>
     </row>
@@ -1647,17 +1647,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 30,74</t>
+          <t>-100,0; 31,69</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>64,5; 551,8</t>
+          <t>72,46; 568,56</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>78,64; 556,26</t>
+          <t>81,62; 520,22</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1667,27 +1667,27 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>166,31; 2220,19</t>
+          <t>161,1; 2097,82</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>164,98; 2240,79</t>
+          <t>164,15; 2201,59</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-93,16; -3,09</t>
+          <t>-92,37; -1,26</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>135,44; 611,12</t>
+          <t>150,83; 620,51</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>143,86; 572,41</t>
+          <t>144,12; 640,21</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-10,61; 10,36</t>
+          <t>-10,34; 10,13</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>6,46; 35,22</t>
+          <t>7,75; 33,82</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-13,64; 5,86</t>
+          <t>-11,88; 6,1</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 14,96</t>
+          <t>-4,19; 15,67</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,57; 30,17</t>
+          <t>3,9; 28,55</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-13,1; 0,0</t>
+          <t>-14,66; 0,0</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 10,25</t>
+          <t>-3,65; 10,09</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>8,76; 27,73</t>
+          <t>8,79; 27,6</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-9,34; 1,79</t>
+          <t>-8,46; 1,95</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>6,06; —</t>
+          <t>22,33; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-7,41; —</t>
+          <t>-30,0; —</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1893,12 +1893,12 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-66,76; 769,1</t>
+          <t>-56,64; 621,44</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>58,74; 1676,76</t>
+          <t>73,92; 1801,55</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-9,52; 4,31</t>
+          <t>-9,64; 4,31</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 15,27</t>
+          <t>-2,0; 15,43</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 17,48</t>
+          <t>-0,64; 17,15</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 2,97</t>
+          <t>-10,26; 2,76</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>7,17; 29,59</t>
+          <t>7,33; 28,82</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,82; 25,45</t>
+          <t>4,28; 25,21</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 1,37</t>
+          <t>-8,15; 1,06</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>5,14; 18,72</t>
+          <t>4,88; 18,28</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>5,51; 19,49</t>
+          <t>4,63; 18,89</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-86,2; 156,46</t>
+          <t>-87,51; 133,76</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-23,94; 376,89</t>
+          <t>-22,77; 436,87</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-11,6; 454,29</t>
+          <t>-12,97; 413,01</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-88,29; 136,84</t>
+          <t>-90,17; 116,71</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>52,01; 880,11</t>
+          <t>60,22; 871,53</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>37,35; 713,5</t>
+          <t>32,34; 750,7</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-77,04; 41,5</t>
+          <t>-79,05; 28,38</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>46,31; 399,15</t>
+          <t>41,17; 388,95</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>45,28; 416,12</t>
+          <t>35,56; 391,96</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 10,91</t>
+          <t>-3,51; 11,28</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>15,17; 33,61</t>
+          <t>15,59; 33,98</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>64,02; 81,13</t>
+          <t>64,32; 81,13</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-10,06; 5,8</t>
+          <t>-10,4; 6,6</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>11,68; 32,2</t>
+          <t>11,12; 32,67</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>62,17; 79,18</t>
+          <t>61,82; 79,87</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 5,77</t>
+          <t>-4,68; 5,87</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>16,07; 29,91</t>
+          <t>16,61; 30,3</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>66,81; 78,82</t>
+          <t>65,4; 78,25</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-36,98; 224,21</t>
+          <t>-40,69; 249,72</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>127,84; 721,23</t>
+          <t>119,2; 675,15</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>499,91; 1890,39</t>
+          <t>487,16; 1790,23</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-67,33; 88,0</t>
+          <t>-68,72; 99,75</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>70,11; 432,47</t>
+          <t>66,37; 484,78</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>364,22; 1147,7</t>
+          <t>373,1; 1361,74</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-43,45; 80,31</t>
+          <t>-39,79; 85,78</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>122,07; 429,66</t>
+          <t>134,84; 426,19</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>503,37; 1256,0</t>
+          <t>480,85; 1161,23</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 1,65</t>
+          <t>-4,59; 1,27</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>7,84; 15,89</t>
+          <t>7,72; 15,71</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>17,83; 27,53</t>
+          <t>17,62; 26,54</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 2,74</t>
+          <t>-3,47; 2,53</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>8,77; 17,06</t>
+          <t>9,09; 17,39</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>20,17; 30,08</t>
+          <t>20,09; 29,84</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 1,14</t>
+          <t>-3,03; 1,07</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>9,57; 15,22</t>
+          <t>9,73; 15,3</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>20,2; 27,1</t>
+          <t>20,52; 27,43</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-50,66; 29,71</t>
+          <t>-52,23; 22,77</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>85,75; 277,32</t>
+          <t>79,23; 258,15</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>195,16; 490,86</t>
+          <t>191,82; 456,57</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-40,42; 52,99</t>
+          <t>-41,29; 49,25</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>105,21; 330,28</t>
+          <t>109,37; 330,73</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>233,43; 562,85</t>
+          <t>235,84; 601,88</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-40,26; 18,37</t>
+          <t>-37,67; 17,56</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>118,61; 253,58</t>
+          <t>115,9; 257,19</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>242,06; 445,98</t>
+          <t>253,06; 470,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C02-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP19C02-Provincia-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-1,81</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-6,11</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4,03</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-12,3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-8,26</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,89</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-1,81</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-6,11</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,51</t>
+          <t>-3,66</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,17</t>
+          <t>0,79</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-27,63; 0,85</t>
+          <t>-15,65; 7,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-24,58; 3,93</t>
+          <t>-19,7; 1,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,2; 24,39</t>
+          <t>-8,14; 19,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,84; 8,56</t>
+          <t>-27,59; 1,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-19,73; 1,23</t>
+          <t>-24,26; 4,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,2; 17,87</t>
+          <t>-21,06; 10,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-15,9; 1,82</t>
+          <t>-16,82; 1,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-16,57; 0,76</t>
+          <t>-16,07; 0,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 16,04</t>
+          <t>-9,67; 11,62</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-22,0%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-74,21%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>48,86%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-77,08%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-51,75%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5,59%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-22,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-74,21%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>-22,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 217,97</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-91,2; 118,87</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-73,94; 548,52</t>
+          <t>-79,94; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -803,27 +803,27 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-89,05; 140,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-77,64; 693,48</t>
+          <t>-81,1; 201,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-89,81; 55,03</t>
+          <t>-91,55; 56,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-91,02; 29,0</t>
+          <t>-89,09; 40,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-51,35; 270,74</t>
+          <t>-59,54; 186,83</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-2,6</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3,63</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,84</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>3,77</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2,46</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6,32</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-2,6</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3,63</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,86</t>
+          <t>6,68</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4,44</t>
+          <t>4,57</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,11</t>
+          <t>-8,94; 4,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,64</t>
+          <t>-4,09; 12,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,3; 14,71</t>
+          <t>-5,62; 11,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,9; 3,44</t>
+          <t>1,19; 10,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 12,99</t>
+          <t>0,0; 8,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 11,35</t>
+          <t>2,47; 15,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 4,49</t>
+          <t>-3,45; 4,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 8,07</t>
+          <t>-1,27; 8,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 9,64</t>
+          <t>0,24; 10,11</t>
         </is>
       </c>
     </row>
@@ -946,34 +946,34 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-40,7%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>56,77%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>44,49%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-40,7%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>56,77%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>44,71%</t>
-        </is>
-      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
           <t>11,25%</t>
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>130,63%</t>
+          <t>134,57%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 217,94</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>-47,3; 425,59</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>-62,84; 394,46</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 153,12</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-48,66; 492,83</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-53,58; 403,06</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-77,67; 279,68</t>
+          <t>-74,46; 271,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-38,15; 666,02</t>
+          <t>-37,5; 479,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-28,16; 522,47</t>
+          <t>-10,09; 648,27</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>3,59</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,44</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4,42</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-4,38</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>3,29</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,48</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3,59</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,44</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,49</t>
+          <t>-0,47</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,06</t>
+          <t>2,02</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-15,47; 1,93</t>
+          <t>-1,88; 11,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 14,98</t>
+          <t>-3,6; 8,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,14; 9,13</t>
+          <t>-1,83; 14,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 12,35</t>
+          <t>-15,62; 1,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 6,78</t>
+          <t>-7,93; 17,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 14,89</t>
+          <t>-10,44; 8,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 4,72</t>
+          <t>-5,54; 5,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 8,42</t>
+          <t>-3,43; 8,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 8,71</t>
+          <t>-3,79; 8,78</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>199,64%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>24,21%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>245,51%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-69,07%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>51,94%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-7,54%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>199,64%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>24,21%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>249,29%</t>
+          <t>-7,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>50,07%</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-96,68; 762,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1235,27 +1235,27 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 911,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 470,67</t>
+          <t>-85,0; 661,35</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-75,41; 521,53</t>
+          <t>-70,07; 731,39</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-65,86; 652,17</t>
+          <t>-67,28; 652,14</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>9,36</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6,18</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>9,93</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-1,41</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>8,55</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>7,93</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>9,36</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>6,18</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,18</t>
+          <t>8,49</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8,34</t>
+          <t>9,09</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 4,04</t>
+          <t>3,14; 22,26</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 19,72</t>
+          <t>1,66; 14,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 19,58</t>
+          <t>2,19; 25,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,13; 21,28</t>
+          <t>-8,63; 4,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,62; 13,8</t>
+          <t>-0,68; 18,17</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,46; 27,01</t>
+          <t>-1,14; 19,74</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 10,13</t>
+          <t>-0,78; 9,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,64; 13,31</t>
+          <t>1,76; 13,85</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,95; 17,55</t>
+          <t>2,86; 17,8</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-35,59%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>215,66%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>200,03%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>inf%</t>
+          <t>214,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>418,94%</t>
+          <t>456,66%</t>
         </is>
       </c>
     </row>
@@ -1436,12 +1436,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-45,19; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-56,7; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1451,27 +1451,27 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-44,23; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-54,35; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-60,26; —</t>
+          <t>-73,33; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,63; —</t>
+          <t>-10,14; —</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-7,47; —</t>
+          <t>12,7; —</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-7,78</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>61,9</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>61,56</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-16,96</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>48,31</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>48,44</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-7,78</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>61,9</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>61,57</t>
+          <t>48,72</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>54,76</t>
+          <t>54,84</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-33,04; -1,62</t>
+          <t>-21,95; 3,52</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>23,59; 70,58</t>
+          <t>37,26; 79,74</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>27,19; 64,25</t>
+          <t>43,3; 75,67</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-22,8; 3,56</t>
+          <t>-32,92; -1,71</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>37,42; 78,74</t>
+          <t>20,98; 68,45</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>44,55; 77,1</t>
+          <t>28,66; 64,29</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-23,85; -2,53</t>
+          <t>-24,45; -2,79</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>36,04; 68,31</t>
+          <t>38,02; 70,28</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>41,66; 65,53</t>
+          <t>41,64; 66,48</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-62,31%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>496,02%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>493,29%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-72,68%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>207,02%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>207,56%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-62,31%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>496,02%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>493,39%</t>
+          <t>208,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>298,89%</t>
+          <t>299,3%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 31,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>72,46; 568,56</t>
+          <t>136,23; 2166,75</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>81,62; 520,22</t>
+          <t>156,83; 2257,71</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 44,03</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>161,1; 2097,82</t>
+          <t>65,32; 531,54</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>164,15; 2201,59</t>
+          <t>80,51; 513,12</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-92,37; -1,26</t>
+          <t>-93,07; -12,54</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>150,83; 620,51</t>
+          <t>138,93; 596,87</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>144,12; 640,21</t>
+          <t>146,44; 607,6</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>4,41</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>15,83</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-4,19</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>0,95</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>20,65</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-1,37</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>4,41</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>15,83</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-4,19</t>
+          <t>-1,04</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-2,74</t>
+          <t>-2,44</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-10,34; 10,13</t>
+          <t>-4,17; 15,75</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>7,75; 33,82</t>
+          <t>4,49; 28,28</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-11,88; 6,1</t>
+          <t>-12,77; 0,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 15,67</t>
+          <t>-9,74; 9,76</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,9; 28,55</t>
+          <t>6,18; 36,07</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-14,66; 0,0</t>
+          <t>-11,56; 8,21</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 10,09</t>
+          <t>-3,97; 9,89</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>8,79; 27,6</t>
+          <t>9,45; 28,09</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 1,95</t>
+          <t>-8,92; 2,39</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>105,27%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>378,32%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>17,57%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>381,56%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-25,28%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>105,27%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>378,32%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-19,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-57,54%</t>
+          <t>-51,12%</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>22,33; —</t>
+          <t>-16,29; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-30,0; —</t>
+          <t>17,76; —</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1893,12 +1893,12 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-56,64; 621,44</t>
+          <t>-65,44; 548,41</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>73,92; 1801,55</t>
+          <t>83,79; 1752,5</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-3,38</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>17,65</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>14,6</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>-2,74</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>6,45</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>8,22</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-3,38</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>17,65</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,79</t>
+          <t>9,66</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>11,45</t>
+          <t>12,48</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 4,31</t>
+          <t>-10,41; 2,71</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 15,43</t>
+          <t>8,0; 29,16</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 17,15</t>
+          <t>4,06; 27,66</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-10,26; 2,76</t>
+          <t>-10,16; 3,51</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>7,33; 28,82</t>
+          <t>-1,62; 14,79</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,28; 25,21</t>
+          <t>0,36; 18,84</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 1,06</t>
+          <t>-7,91; 1,68</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>4,88; 18,28</t>
+          <t>5,08; 19,14</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>4,63; 18,89</t>
+          <t>5,96; 20,03</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-46,71%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>244,14%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>201,92%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>-36,41%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>85,8%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>109,33%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-46,71%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>244,14%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>190,82%</t>
+          <t>128,54%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>155,34%</t>
+          <t>169,32%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-87,51; 133,76</t>
+          <t>-91,08; 116,23</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-22,77; 436,87</t>
+          <t>60,62; 835,37</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-12,97; 413,01</t>
+          <t>27,89; 760,01</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-90,17; 116,71</t>
+          <t>-89,25; 127,61</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>60,22; 871,53</t>
+          <t>-22,18; 390,45</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>32,34; 750,7</t>
+          <t>-8,36; 456,87</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-79,05; 28,38</t>
+          <t>-77,77; 50,13</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>41,17; 388,95</t>
+          <t>41,99; 399,05</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>35,56; 391,96</t>
+          <t>54,0; 428,88</t>
         </is>
       </c>
     </row>
@@ -2136,32 +2136,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-1,97</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>21,35</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>72,06</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>3,52</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>24,59</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>73,35</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-1,97</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>21,35</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>71,64</t>
+          <t>74,29</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>72,64</t>
+          <t>73,29</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 11,28</t>
+          <t>-9,62; 6,29</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>15,59; 33,98</t>
+          <t>11,72; 32,98</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>64,32; 81,13</t>
+          <t>62,64; 80,08</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-10,4; 6,6</t>
+          <t>-4,29; 11,31</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>11,12; 32,67</t>
+          <t>14,75; 33,99</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>61,82; 79,87</t>
+          <t>64,68; 81,91</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 5,87</t>
+          <t>-4,39; 6,59</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>16,61; 30,3</t>
+          <t>16,01; 30,51</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>65,4; 78,25</t>
+          <t>66,48; 78,59</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-17,74%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>192,32%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>649,2%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>44,46%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>310,89%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>927,46%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-17,74%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>192,32%</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>645,33%</t>
+          <t>939,39%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>769,96%</t>
+          <t>776,89%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-40,69; 249,72</t>
+          <t>-67,38; 89,94</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>119,2; 675,15</t>
+          <t>66,82; 459,01</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>487,16; 1790,23</t>
+          <t>358,58; 1157,4</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-68,72; 99,75</t>
+          <t>-41,36; 225,18</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>66,37; 484,78</t>
+          <t>105,51; 648,83</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>373,1; 1361,74</t>
+          <t>467,17; 1787,71</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-39,79; 85,78</t>
+          <t>-36,04; 91,65</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>134,84; 426,19</t>
+          <t>121,92; 456,18</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>480,85; 1161,23</t>
+          <t>519,38; 1299,48</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>-0,33</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>12,87</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>27,04</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>-1,57</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>11,63</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>22,37</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>-0,33</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>12,87</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>24,81</t>
+          <t>24,02</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>23,69</t>
+          <t>25,62</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 1,27</t>
+          <t>-3,09; 2,72</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>7,72; 15,71</t>
+          <t>8,86; 16,75</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>17,62; 26,54</t>
+          <t>22,45; 32,05</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 2,53</t>
+          <t>-4,53; 1,55</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>9,09; 17,39</t>
+          <t>7,55; 15,62</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>20,09; 29,84</t>
+          <t>19,22; 28,72</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 1,07</t>
+          <t>-3,07; 1,21</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>9,73; 15,3</t>
+          <t>9,25; 14,93</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>20,52; 27,43</t>
+          <t>22,4; 29,03</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>-4,97%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>192,91%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>405,14%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>-21,42%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>158,58%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>304,99%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>-4,97%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>192,91%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>371,71%</t>
+          <t>327,49%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>338,43%</t>
+          <t>366,09%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-52,23; 22,77</t>
+          <t>-39,01; 51,73</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>79,23; 258,15</t>
+          <t>109,15; 321,82</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>191,82; 456,57</t>
+          <t>257,44; 635,23</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-41,29; 49,25</t>
+          <t>-50,04; 28,52</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>109,37; 330,73</t>
+          <t>81,22; 271,1</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>235,84; 601,88</t>
+          <t>217,28; 526,78</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-37,67; 17,56</t>
+          <t>-37,85; 20,54</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>115,9; 257,19</t>
+          <t>112,14; 258,28</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>253,06; 470,21</t>
+          <t>272,29; 503,43</t>
         </is>
       </c>
     </row>
